--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
@@ -232,7 +232,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1039,7 +1041,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Parcelas e inadimplência · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
         <v/>
@@ -2116,7 +2118,7 @@
     <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações e régua de cobrança</t>
@@ -2262,8 +2264,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2290,7 +2293,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Casos (entrada)</t>
@@ -8898,7 +8901,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:J204"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="J5:J204">
@@ -8945,7 +8949,7 @@
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Parcelas</t>
@@ -26036,8 +26040,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:L404"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:L404">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
@@ -23,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -249,19 +250,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -277,7 +278,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -287,7 +288,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,7 +298,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,10 +309,10 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -839,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1000,17 +1001,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1107,22 +1120,22 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="14">
         <f>SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$H$5:$H$404,"A vencer")+SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$H$5:$H$404,"Vencida")</f>
-        <v>56730</v>
+        <v>55330</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="15">
         <f>SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$H$5:$H$404,"Vencida")</f>
-        <v>14480</v>
+        <v>13080</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="16">
         <f>COUNTIFS(Parcelas!$H$5:$H$404,"Vencida")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="17">
         <f>IFERROR(G5/(G5+SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$H$5:$H$404,"Paga")),0)</f>
-        <v>0.0505604245958309</v>
+        <v>0.045896347240254</v>
       </c>
       <c r="L5" s="12" t="n"/>
     </row>
@@ -1185,7 +1198,7 @@
       </c>
       <c r="D11" s="26">
         <f>IF(Config!$C$10="","",IFERROR(C11/$G$5,0))</f>
-        <v>0.136740331491713</v>
+        <v>0.151376146788991</v>
       </c>
       <c r="E11" s="27" t="str">
         <f>IF(Config!$C$10="","",Config!$B$10)</f>
@@ -1235,7 +1248,7 @@
       </c>
       <c r="D13" s="26">
         <f>IF(Config!$C$12="","",IFERROR(C13/$G$5,0))</f>
-        <v>0.103591160220994</v>
+        <v>0.114678899082569</v>
       </c>
       <c r="E13" s="27" t="str">
         <f>IF(Config!$C$12="","",Config!$B$12)</f>
@@ -1252,15 +1265,15 @@
       </c>
       <c r="B14" s="24">
         <f>IF(Config!$C$13="","",COUNTIFS(Parcelas!$K$5:$K$404,Config!$C$13))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="25">
         <f>IF(Config!$C$13="","",SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$K$5:$K$404,Config!$C$13))</f>
-        <v>11000</v>
+        <v>9600</v>
       </c>
       <c r="D14" s="26">
         <f>IF(Config!$C$13="","",IFERROR(C14/$G$5,0))</f>
-        <v>0.759668508287293</v>
+        <v>0.73394495412844</v>
       </c>
       <c r="E14" s="27" t="str">
         <f>IF(Config!$C$13="","",Config!$B$13)</f>
@@ -1447,27 +1460,27 @@
       </c>
       <c r="B22" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Fernanda Castro</v>
+        <v>Oficina Mecânica Central</v>
       </c>
       <c r="C22" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>5211189-81.2025.8.26.0412</v>
+        <v>6184138-13.2026.8.26.0378</v>
       </c>
       <c r="D22" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46066.0</v>
+        <v>46192.0</v>
       </c>
       <c r="F22" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G22" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>213</v>
+        <v>87</v>
       </c>
       <c r="H22" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,3)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,3),Parcelas!$M$5:$M$404,0)),""),"")</f>
@@ -1487,11 +1500,11 @@
       </c>
       <c r="B23" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Oficina Mecânica Central</v>
+        <v>Patrícia Gomes</v>
       </c>
       <c r="C23" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>6184138-13.2026.8.26.0378</v>
+        <v>9616569-91.2026.8.26.0079</v>
       </c>
       <c r="D23" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
@@ -1499,15 +1512,15 @@
       </c>
       <c r="E23" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46192.0</v>
+        <v>46248.0</v>
       </c>
       <c r="F23" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="G23" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="H23" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,4)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,4),Parcelas!$M$5:$M$404,0)),""),"")</f>
@@ -1527,27 +1540,27 @@
       </c>
       <c r="B24" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Patrícia Gomes</v>
+        <v>Agência Prisma</v>
       </c>
       <c r="C24" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>9616569-91.2026.8.26.0079</v>
+        <v>9362688-24.2025.8.26.0436</v>
       </c>
       <c r="D24" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46248.0</v>
+        <v>46244.0</v>
       </c>
       <c r="F24" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="G24" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H24" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,5)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,5),Parcelas!$M$5:$M$404,0)),""),"")</f>
@@ -1567,35 +1580,35 @@
       </c>
       <c r="B25" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Agência Prisma</v>
+        <v>Helena Duarte</v>
       </c>
       <c r="C25" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>9362688-24.2025.8.26.0436</v>
+        <v>7679821-77.2026.8.26.0265</v>
       </c>
       <c r="D25" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46244.0</v>
+        <v>46262.0</v>
       </c>
       <c r="F25" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="G25" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H25" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>30 dias ou mais</v>
+        <v>15 a 29 dias</v>
       </c>
       <c r="I25" s="27" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,6)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$M$5:$M$404,6),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Ligação ou reunião para combinar um plano de pagamento; registrar por escrito o que foi combinado e a nova data.</v>
+        <v>E-mail com o demonstrativo das parcelas em aberto e proposta de renegociação (nova data ou divisão do valor).</v>
       </c>
       <c r="J25" s="21" t="n"/>
       <c r="K25" s="21" t="n"/>
@@ -1607,35 +1620,35 @@
       </c>
       <c r="B26" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Helena Duarte</v>
+        <v>Agência Prisma</v>
       </c>
       <c r="C26" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>7679821-77.2026.8.26.0265</v>
+        <v>9362688-24.2025.8.26.0436</v>
       </c>
       <c r="D26" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46262.0</v>
+        <v>46275.0</v>
       </c>
       <c r="F26" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1500</v>
+        <v>1980</v>
       </c>
       <c r="G26" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H26" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>15 a 29 dias</v>
+        <v>1 a 6 dias</v>
       </c>
       <c r="I26" s="27" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,7)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$M$5:$M$404,7),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>E-mail com o demonstrativo das parcelas em aberto e proposta de renegociação (nova data ou divisão do valor).</v>
+        <v>Lembrete gentil por WhatsApp ou e-mail: confirmar se o boleto ou o link de pagamento chegou e reenviar, se preciso.</v>
       </c>
       <c r="J26" s="21" t="n"/>
       <c r="K26" s="21" t="n"/>
@@ -1645,37 +1658,37 @@
       <c r="A27" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="23" t="str">
+      <c r="B27" s="23">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Agência Prisma</v>
-      </c>
-      <c r="C27" s="23" t="str">
+        <v/>
+      </c>
+      <c r="C27" s="23">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>9362688-24.2025.8.26.0436</v>
+        <v/>
       </c>
       <c r="D27" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$C$5:$C$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="E27" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>46275.0</v>
+        <v/>
       </c>
       <c r="F27" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1980</v>
+        <v/>
       </c>
       <c r="G27" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$I$5:$I$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>4</v>
-      </c>
-      <c r="H27" s="24" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>1 a 6 dias</v>
-      </c>
-      <c r="I27" s="27" t="str">
+        <v/>
+      </c>
+      <c r="I27" s="27">
         <f>IFERROR(IF(LARGE(Parcelas!$M$5:$M$404,8)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$M$5:$M$404,8),Parcelas!$M$5:$M$404,0)),""),"")</f>
-        <v>Lembrete gentil por WhatsApp ou e-mail: confirmar se o boleto ou o link de pagamento chegou e reenviar, se preciso.</v>
+        <v/>
       </c>
       <c r="J27" s="21" t="n"/>
       <c r="K27" s="21" t="n"/>
@@ -2154,9 +2167,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="33" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -3924,11 +3936,11 @@
       </c>
       <c r="E40" s="24">
         <f>IF(A40="","",COUNTIFS(Parcelas!$A$5:$A$404,A40))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" s="25">
         <f>IF(A40="","",SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$A$5:$A$404,A40))</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="G40" s="25">
         <f>IF(A40="","",SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$A$5:$A$404,A40,Parcelas!$H$5:$H$404,"Paga"))</f>
@@ -3936,15 +3948,15 @@
       </c>
       <c r="H40" s="25">
         <f>IF(A40="","",F40-G40)</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I40" s="25">
         <f>IF(A40="","",SUMIFS(Parcelas!$E$5:$E$404,Parcelas!$A$5:$A$404,A40,Parcelas!$H$5:$H$404,"Vencida"))</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="J40" s="25">
         <f>IF(OR(A40="",E40=0),"",D40-F40)</f>
-        <v>-1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -9210,9 +9222,8 @@
       <c r="C8" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="37">
-        <f>TODAY()+21</f>
-        <v>46300.0</v>
+      <c r="D8" s="37" t="n">
+        <v>46300</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>1500</v>
@@ -9265,9 +9276,8 @@
       <c r="C9" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="37">
-        <f>TODAY()+52</f>
-        <v>46331.0</v>
+      <c r="D9" s="37" t="n">
+        <v>46331</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>1500</v>
@@ -9320,9 +9330,8 @@
       <c r="C10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="37">
-        <f>TODAY()+82</f>
-        <v>46361.0</v>
+      <c r="D10" s="37" t="n">
+        <v>46361</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>1500</v>
@@ -9375,9 +9384,8 @@
       <c r="C11" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="37">
-        <f>TODAY()+113</f>
-        <v>46392.0</v>
+      <c r="D11" s="37" t="n">
+        <v>46392</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>1500</v>
@@ -9430,9 +9438,8 @@
       <c r="C12" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="37">
-        <f>TODAY()+144</f>
-        <v>46423.0</v>
+      <c r="D12" s="37" t="n">
+        <v>46423</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>1500</v>
@@ -9485,9 +9492,8 @@
       <c r="C13" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="D13" s="37">
-        <f>TODAY()+172</f>
-        <v>46451.0</v>
+      <c r="D13" s="37" t="n">
+        <v>46451</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>1500</v>
@@ -9540,9 +9546,8 @@
       <c r="C14" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="37">
-        <f>TODAY()+203</f>
-        <v>46482.0</v>
+      <c r="D14" s="37" t="n">
+        <v>46482</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>1500</v>
@@ -9595,9 +9600,8 @@
       <c r="C15" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="37">
-        <f>TODAY()+233</f>
-        <v>46512.0</v>
+      <c r="D15" s="37" t="n">
+        <v>46512</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1500</v>
@@ -9650,9 +9654,8 @@
       <c r="C16" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="37">
-        <f>TODAY()+264</f>
-        <v>46543.0</v>
+      <c r="D16" s="37" t="n">
+        <v>46543</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>1500</v>
@@ -9817,9 +9820,8 @@
       <c r="C19" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="37">
-        <f>TODAY()+14</f>
-        <v>46293.0</v>
+      <c r="D19" s="37" t="n">
+        <v>46293</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>2100</v>
@@ -9872,9 +9874,8 @@
       <c r="C20" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="37">
-        <f>TODAY()+44</f>
-        <v>46323.0</v>
+      <c r="D20" s="37" t="n">
+        <v>46323</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>2100</v>
@@ -10039,9 +10040,8 @@
       <c r="C23" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="37">
-        <f>TODAY()+16</f>
-        <v>46295.0</v>
+      <c r="D23" s="37" t="n">
+        <v>46295</v>
       </c>
       <c r="E23" s="36" t="n">
         <v>1500</v>
@@ -10150,9 +10150,8 @@
       <c r="C25" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="37">
-        <f>TODAY()+3</f>
-        <v>46282.0</v>
+      <c r="D25" s="37" t="n">
+        <v>46282</v>
       </c>
       <c r="E25" s="36" t="n">
         <v>2800</v>
@@ -10205,9 +10204,8 @@
       <c r="C26" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="37">
-        <f>TODAY()+35</f>
-        <v>46314.0</v>
+      <c r="D26" s="37" t="n">
+        <v>46314</v>
       </c>
       <c r="E26" s="36" t="n">
         <v>2800</v>
@@ -10316,9 +10314,8 @@
       <c r="C28" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+      <c r="D28" s="37" t="n">
+        <v>46290</v>
       </c>
       <c r="E28" s="36" t="n">
         <v>2250</v>
@@ -10483,9 +10480,8 @@
       <c r="C31" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
+      <c r="D31" s="37" t="n">
+        <v>46305</v>
       </c>
       <c r="E31" s="36" t="n">
         <v>1100</v>
@@ -10538,9 +10534,8 @@
       <c r="C32" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="37">
-        <f>TODAY()+57</f>
-        <v>46336.0</v>
+      <c r="D32" s="37" t="n">
+        <v>46336</v>
       </c>
       <c r="E32" s="36" t="n">
         <v>1100</v>
@@ -10593,9 +10588,8 @@
       <c r="C33" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="37">
-        <f>TODAY()+87</f>
-        <v>46366.0</v>
+      <c r="D33" s="37" t="n">
+        <v>46366</v>
       </c>
       <c r="E33" s="36" t="n">
         <v>1100</v>
@@ -10648,9 +10642,8 @@
       <c r="C34" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="37">
-        <f>TODAY()+118</f>
-        <v>46397.0</v>
+      <c r="D34" s="37" t="n">
+        <v>46397</v>
       </c>
       <c r="E34" s="36" t="n">
         <v>1100</v>
@@ -10703,9 +10696,8 @@
       <c r="C35" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="37">
-        <f>TODAY()+149</f>
-        <v>46428.0</v>
+      <c r="D35" s="37" t="n">
+        <v>46428</v>
       </c>
       <c r="E35" s="36" t="n">
         <v>1100</v>
@@ -10758,9 +10750,8 @@
       <c r="C36" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="37">
-        <f>TODAY()+177</f>
-        <v>46456.0</v>
+      <c r="D36" s="37" t="n">
+        <v>46456</v>
       </c>
       <c r="E36" s="36" t="n">
         <v>1100</v>
@@ -10813,9 +10804,8 @@
       <c r="C37" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="D37" s="37">
-        <f>TODAY()+208</f>
-        <v>46487.0</v>
+      <c r="D37" s="37" t="n">
+        <v>46487</v>
       </c>
       <c r="E37" s="36" t="n">
         <v>1100</v>
@@ -10868,9 +10858,8 @@
       <c r="C38" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="37">
-        <f>TODAY()+238</f>
-        <v>46517.0</v>
+      <c r="D38" s="37" t="n">
+        <v>46517</v>
       </c>
       <c r="E38" s="36" t="n">
         <v>1100</v>
@@ -10923,9 +10912,8 @@
       <c r="C39" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="D39" s="37">
-        <f>TODAY()+269</f>
-        <v>46548.0</v>
+      <c r="D39" s="37" t="n">
+        <v>46548</v>
       </c>
       <c r="E39" s="36" t="n">
         <v>1100</v>
@@ -10978,9 +10966,8 @@
       <c r="C40" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="37">
-        <f>TODAY()+299</f>
-        <v>46578.0</v>
+      <c r="D40" s="37" t="n">
+        <v>46578</v>
       </c>
       <c r="E40" s="36" t="n">
         <v>1100</v>
@@ -11145,9 +11132,8 @@
       <c r="C43" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="37">
-        <f>TODAY()-180</f>
-        <v>46099.0</v>
+      <c r="D43" s="37" t="n">
+        <v>46099</v>
       </c>
       <c r="E43" s="36" t="n">
         <v>2100</v>
@@ -11200,9 +11186,8 @@
       <c r="C44" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="37">
-        <f>TODAY()-150</f>
-        <v>46129.0</v>
+      <c r="D44" s="37" t="n">
+        <v>46129</v>
       </c>
       <c r="E44" s="36" t="n">
         <v>2100</v>
@@ -12431,9 +12416,8 @@
       <c r="C66" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="37">
-        <f>TODAY()+10</f>
-        <v>46289.0</v>
+      <c r="D66" s="37" t="n">
+        <v>46289</v>
       </c>
       <c r="E66" s="36" t="n">
         <v>2700</v>
@@ -13214,9 +13198,8 @@
       <c r="C80" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D80" s="37">
-        <f>TODAY()-31</f>
-        <v>46248.0</v>
+      <c r="D80" s="37" t="n">
+        <v>46248</v>
       </c>
       <c r="E80" s="36" t="n">
         <v>2100</v>
@@ -13941,9 +13924,8 @@
       <c r="C93" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D93" s="37">
-        <f>TODAY()-87</f>
-        <v>46192.0</v>
+      <c r="D93" s="37" t="n">
+        <v>46192</v>
       </c>
       <c r="E93" s="36" t="n">
         <v>1500</v>
@@ -14724,9 +14706,8 @@
       <c r="C107" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="D107" s="37">
-        <f>TODAY()-35</f>
-        <v>46244.0</v>
+      <c r="D107" s="37" t="n">
+        <v>46244</v>
       </c>
       <c r="E107" s="36" t="n">
         <v>1800</v>
@@ -14779,9 +14760,8 @@
       <c r="C108" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="D108" s="37">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
+      <c r="D108" s="37" t="n">
+        <v>46275</v>
       </c>
       <c r="E108" s="36" t="n">
         <v>1980</v>
@@ -15058,9 +15038,8 @@
       <c r="C113" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D113" s="37">
-        <f>TODAY()-17</f>
-        <v>46262.0</v>
+      <c r="D113" s="37" t="n">
+        <v>46262</v>
       </c>
       <c r="E113" s="36" t="n">
         <v>1500</v>
@@ -15113,9 +15092,8 @@
       <c r="C114" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D114" s="37">
-        <f>TODAY()+14</f>
-        <v>46293.0</v>
+      <c r="D114" s="37" t="n">
+        <v>46293</v>
       </c>
       <c r="E114" s="36" t="n">
         <v>1500</v>
@@ -17342,52 +17320,53 @@
     <row r="154">
       <c r="A154" s="32" t="inlineStr">
         <is>
-          <t>5211189-81.2025.8.26.0412</t>
+          <t>6161129-80.2025.8.26.0663</t>
         </is>
       </c>
       <c r="B154" s="23" t="str">
         <f>IF(A154="","",IFERROR(INDEX(Casos!$B$5:$B$204,MATCH(A154,Casos!$A$5:$A$204,0)),""))</f>
-        <v>Fernanda Castro</v>
+        <v>José Antônio Ribeiro</v>
       </c>
       <c r="C154" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D154" s="37">
-        <f>TODAY()-213</f>
-        <v>46066.0</v>
+        <v>1</v>
+      </c>
+      <c r="D154" s="37" t="n">
+        <v>46203</v>
       </c>
       <c r="E154" s="36" t="n">
-        <v>1400</v>
+        <v>6000</v>
       </c>
       <c r="F154" s="34" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G154" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G154" s="37" t="n">
+        <v>46203</v>
+      </c>
       <c r="H154" s="24" t="str">
         <f>IF(A154="","",IF(F154="Sim","Paga",IF(D154="","Sem vencimento",IF(D154&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="I154" s="30">
         <f>IF(H154="Vencida",Config!$B$5-D154,"")</f>
-        <v>213</v>
+        <v/>
       </c>
       <c r="J154" s="30">
         <f>IF(H154="A vencer",D154-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="K154" s="24" t="str">
+      <c r="K154" s="24">
         <f>IF(H154&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;I154)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;I154))))</f>
-        <v>30 dias ou mais</v>
-      </c>
-      <c r="L154" s="23" t="str">
+        <v/>
+      </c>
+      <c r="L154" s="23">
         <f>IF(H154&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;I154)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;I154))))</f>
-        <v>Ligação ou reunião para combinar um plano de pagamento; registrar por escrito o que foi combinado e a nova data.</v>
+        <v/>
       </c>
       <c r="M154" s="38">
         <f>IF(H154="Vencida",E154*I154+ROW()/100000,0)</f>
-        <v>298200.00154</v>
+        <v>0</v>
       </c>
       <c r="N154" s="38">
         <f>IF(AND(H154="A vencer",J154&lt;=Config!$B$7),100000-J154-ROW()/100000,0)</f>
@@ -17397,21 +17376,21 @@
     <row r="155">
       <c r="A155" s="32" t="inlineStr">
         <is>
-          <t>6161129-80.2025.8.26.0663</t>
+          <t>9420478-99.2025.8.26.0491</t>
         </is>
       </c>
       <c r="B155" s="23" t="str">
         <f>IF(A155="","",IFERROR(INDEX(Casos!$B$5:$B$204,MATCH(A155,Casos!$A$5:$A$204,0)),""))</f>
-        <v>José Antônio Ribeiro</v>
+        <v>Ana Beatriz Moreira</v>
       </c>
       <c r="C155" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D155" s="37" t="n">
-        <v>46203</v>
+        <v>45684</v>
       </c>
       <c r="E155" s="36" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F155" s="34" t="inlineStr">
         <is>
@@ -17419,7 +17398,7 @@
         </is>
       </c>
       <c r="G155" s="37" t="n">
-        <v>46203</v>
+        <v>45684</v>
       </c>
       <c r="H155" s="24" t="str">
         <f>IF(A155="","",IF(F155="Sim","Paga",IF(D155="","Sem vencimento",IF(D155&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17461,13 +17440,13 @@
         <v>Ana Beatriz Moreira</v>
       </c>
       <c r="C156" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" s="37" t="n">
-        <v>45684</v>
+        <v>46101</v>
       </c>
       <c r="E156" s="36" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="F156" s="34" t="inlineStr">
         <is>
@@ -17475,7 +17454,7 @@
         </is>
       </c>
       <c r="G156" s="37" t="n">
-        <v>45684</v>
+        <v>46101</v>
       </c>
       <c r="H156" s="24" t="str">
         <f>IF(A156="","",IF(F156="Sim","Paga",IF(D156="","Sem vencimento",IF(D156&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17507,35 +17486,19 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="32" t="inlineStr">
-        <is>
-          <t>9420478-99.2025.8.26.0491</t>
-        </is>
-      </c>
-      <c r="B157" s="23" t="str">
+      <c r="A157" s="32" t="n"/>
+      <c r="B157" s="23">
         <f>IF(A157="","",IFERROR(INDEX(Casos!$B$5:$B$204,MATCH(A157,Casos!$A$5:$A$204,0)),""))</f>
-        <v>Ana Beatriz Moreira</v>
-      </c>
-      <c r="C157" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D157" s="37" t="n">
-        <v>46101</v>
-      </c>
-      <c r="E157" s="36" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F157" s="34" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G157" s="37" t="n">
-        <v>46101</v>
-      </c>
-      <c r="H157" s="24" t="str">
+        <v/>
+      </c>
+      <c r="C157" s="34" t="n"/>
+      <c r="D157" s="37" t="n"/>
+      <c r="E157" s="36" t="n"/>
+      <c r="F157" s="34" t="n"/>
+      <c r="G157" s="37" t="n"/>
+      <c r="H157" s="24">
         <f>IF(A157="","",IF(F157="Sim","Paga",IF(D157="","Sem vencimento",IF(D157&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v/>
       </c>
       <c r="I157" s="30">
         <f>IF(H157="Vencida",Config!$B$5-D157,"")</f>
@@ -27445,7 +27408,7 @@
     <row r="406">
       <c r="A406" s="28" t="inlineStr">
         <is>
-          <t>Vermelho: vencida. Amarelo: vence na janela curta. Verde: paga. Data do pagamento em vermelho: marcada como paga sem data. No exemplo, as parcelas pagas têm data fixa (cada uma é uma entrada do caixa, planilha 09) e as em aberto têm vencimento relativo a hoje.</t>
+          <t>Vermelho: vencida. Amarelo: vence na janela curta. Verde: paga. Data do pagamento em vermelho: marcada como paga sem data. No exemplo, todas as datas são fixas na data-base de 14/09/2026, para os números fecharem com o caixa (planilha 09) e com a carteira (13).</t>
         </is>
       </c>
     </row>
@@ -27473,19 +27436,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Casos!$A$5,0,0,MAX(1,COUNTA(Casos!$A$5:$A$204)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/14-parcelas-e-inadimplencia.xlsx
@@ -989,7 +989,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A34:G41">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(ISNUMBER($G34),$G34&lt;=Config!$B$6)</formula>
+      <formula>AND(ISNUMBER($G34),$G34&lt;=INDIRECT("Config!$B$6"))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27424,7 +27424,7 @@
       <formula>$H5="Vencida"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND($H5="A vencer",$J5&lt;=Config!$B$6)</formula>
+      <formula>AND($H5="A vencer",$J5&lt;=INDIRECT("Config!$B$6"))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
       <formula>$H5="Paga"</formula>
